--- a/artfynd/A 9114-2024 artfynd.xlsx
+++ b/artfynd/A 9114-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,257 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123301102</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56691</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kilmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>616466</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6976014</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>796</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Upplysande ungfåglar i myrkant</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123301078</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kilen, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>616494</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6975995</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9114-2024 artfynd.xlsx
+++ b/artfynd/A 9114-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301102</v>
+        <v>123301078</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>90955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilmyran, Ång</t>
+          <t>Kilen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616466</v>
+        <v>616494</v>
       </c>
       <c r="R3" t="n">
-        <v>6976014</v>
+        <v>6975995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +857,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -871,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Upplysande ungfåglar i myrkant</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123301078</v>
+        <v>123301102</v>
       </c>
       <c r="B4" t="n">
-        <v>90952</v>
+        <v>56694</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,38 +920,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilen, Ång</t>
+          <t>Kilmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616494</v>
+        <v>616466</v>
       </c>
       <c r="R4" t="n">
-        <v>6975995</v>
+        <v>6976014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +982,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>796</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -997,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1002,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Upplysande ungfåglar i myrkant</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 9114-2024 artfynd.xlsx
+++ b/artfynd/A 9114-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301078</v>
+        <v>123301102</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>56694</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilen, Ång</t>
+          <t>Kilmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616494</v>
+        <v>616466</v>
       </c>
       <c r="R3" t="n">
-        <v>6975995</v>
+        <v>6976014</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +861,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>796</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Upplysande ungfåglar i myrkant</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123301102</v>
+        <v>123301078</v>
       </c>
       <c r="B4" t="n">
-        <v>56694</v>
+        <v>90957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,42 +929,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilmyran, Ång</t>
+          <t>Kilen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616466</v>
+        <v>616494</v>
       </c>
       <c r="R4" t="n">
-        <v>6976014</v>
+        <v>6975995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +987,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -992,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,12 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Upplysande ungfåglar i myrkant</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 9114-2024 artfynd.xlsx
+++ b/artfynd/A 9114-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301102</v>
+        <v>123301078</v>
       </c>
       <c r="B3" t="n">
-        <v>56694</v>
+        <v>90963</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilmyran, Ång</t>
+          <t>Kilen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616466</v>
+        <v>616494</v>
       </c>
       <c r="R3" t="n">
-        <v>6976014</v>
+        <v>6975995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +857,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -871,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Upplysande ungfåglar i myrkant</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123301078</v>
+        <v>123301102</v>
       </c>
       <c r="B4" t="n">
-        <v>90957</v>
+        <v>56694</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,38 +920,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilen, Ång</t>
+          <t>Kilmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616494</v>
+        <v>616466</v>
       </c>
       <c r="R4" t="n">
-        <v>6975995</v>
+        <v>6976014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +982,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>796</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -997,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1002,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Upplysande ungfåglar i myrkant</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 9114-2024 artfynd.xlsx
+++ b/artfynd/A 9114-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301078</v>
+        <v>123301102</v>
       </c>
       <c r="B3" t="n">
-        <v>90963</v>
+        <v>56694</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilen, Ång</t>
+          <t>Kilmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616494</v>
+        <v>616466</v>
       </c>
       <c r="R3" t="n">
-        <v>6975995</v>
+        <v>6976014</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +861,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>796</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Upplysande ungfåglar i myrkant</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123301102</v>
+        <v>123301078</v>
       </c>
       <c r="B4" t="n">
-        <v>56694</v>
+        <v>90966</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,42 +929,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilmyran, Ång</t>
+          <t>Kilen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616466</v>
+        <v>616494</v>
       </c>
       <c r="R4" t="n">
-        <v>6976014</v>
+        <v>6975995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +987,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -992,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,12 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Upplysande ungfåglar i myrkant</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 9114-2024 artfynd.xlsx
+++ b/artfynd/A 9114-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>123301102</v>
       </c>
       <c r="B3" t="n">
-        <v>56694</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>123301078</v>
       </c>
       <c r="B4" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 9114-2024 artfynd.xlsx
+++ b/artfynd/A 9114-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>123301102</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>56703</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>123301078</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 9114-2024 artfynd.xlsx
+++ b/artfynd/A 9114-2024 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>123301078</v>
       </c>
       <c r="B4" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 9114-2024 artfynd.xlsx
+++ b/artfynd/A 9114-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301102</v>
+        <v>123301078</v>
       </c>
       <c r="B3" t="n">
-        <v>56703</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilmyran, Ång</t>
+          <t>Kilen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616466</v>
+        <v>616494</v>
       </c>
       <c r="R3" t="n">
-        <v>6976014</v>
+        <v>6975995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +857,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -871,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Upplysande ungfåglar i myrkant</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123301078</v>
+        <v>123301102</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>56703</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,38 +920,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilen, Ång</t>
+          <t>Kilmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616494</v>
+        <v>616466</v>
       </c>
       <c r="R4" t="n">
-        <v>6975995</v>
+        <v>6976014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +982,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>796</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -997,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1002,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Upplysande ungfåglar i myrkant</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 9114-2024 artfynd.xlsx
+++ b/artfynd/A 9114-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301078</v>
+        <v>123301102</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>56703</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilen, Ång</t>
+          <t>Kilmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616494</v>
+        <v>616466</v>
       </c>
       <c r="R3" t="n">
-        <v>6975995</v>
+        <v>6976014</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +861,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>796</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Upplysande ungfåglar i myrkant</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123301102</v>
+        <v>123301078</v>
       </c>
       <c r="B4" t="n">
-        <v>56703</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,42 +929,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilmyran, Ång</t>
+          <t>Kilen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616466</v>
+        <v>616494</v>
       </c>
       <c r="R4" t="n">
-        <v>6976014</v>
+        <v>6975995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +987,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -992,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,12 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Upplysande ungfåglar i myrkant</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
